--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Canone unico patrimoniale.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Canone unico patrimoniale.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="102">
   <si>
     <r>
       <t xml:space="preserve">
@@ -407,7 +407,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -577,7 +577,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> È possibile richiedere la domiciliazione delle rette direttamente sul tuo conto corrente. Per maggiori informazioni, [visita questo sito](URL). 
+      <t xml:space="preserve"> È possibile richiedere la domiciliazione delle rette direttamente sul tuo conto corrente. Per maggiori informazioni, [visita questo sito](URL).
 Se hai già provveduto a pagare l'avviso o se hai richiesto la domiciliazione sul conto corrente, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
@@ -680,7 +680,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">  è stata accolta.
+      <t xml:space="preserve"> è stata accolta.
 </t>
     </r>
     <r>
@@ -778,7 +778,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> non è stata accolta. 
+      <t xml:space="preserve"> non è stata accolta.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -806,7 +806,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -865,7 +865,7 @@
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
-    <t>Vedi ricevuta</t>
+    <t>Vai alla ricevuta</t>
   </si>
   <si>
     <r>
@@ -885,7 +885,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -959,14 +959,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -1807,13 +1799,13 @@
         <v>57</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>57</v>
